--- a/outputs/speech-landing/uniqore-speech-analysis-demo-report.xlsx
+++ b/outputs/speech-landing/uniqore-speech-analysis-demo-report.xlsx
@@ -623,7 +623,8 @@
         <x:v>Average score for eligible reps</x:v>
       </x:c>
       <x:c r="B7" s="27" t="n">
-        <x:v>74.66666666666667</x:v>
+        <x:f>AVERAGE('Rep Coaching'!B6:B9)</x:f>
+        <x:v>68.75</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Fixed 0–100 rubric; code calculates the score</x:v>
